--- a/發電廠_案例資料收集.xlsx
+++ b/發電廠_案例資料收集.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\Kuo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A94CC557-4043-4246-97BC-CBF379AAE25A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E3048BE-A9C7-43C6-A7AB-FA311EE9B444}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1636,6 +1636,9 @@
       <c r="G25" s="5"/>
     </row>
     <row r="26" spans="1:10" ht="13.2">
+      <c r="B26">
+        <v>1111111</v>
+      </c>
       <c r="D26" s="4"/>
       <c r="G26" s="5"/>
     </row>
